--- a/artfynd/A 22559-2026 artfynd.xlsx
+++ b/artfynd/A 22559-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -788,6 +788,205 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>133930757</v>
+      </c>
+      <c r="B3" t="n">
+        <v>101348</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Grankärret, Grankärret, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>555719</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6337493</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>133930852</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58119</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Grankärret, Grankärret, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>555700</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6337491</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22559-2026 artfynd.xlsx
+++ b/artfynd/A 22559-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133477377</v>
       </c>
       <c r="B2" t="n">
-        <v>9412</v>
+        <v>9420</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>133930757</v>
       </c>
       <c r="B3" t="n">
-        <v>101348</v>
+        <v>101376</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>133930852</v>
       </c>
       <c r="B4" t="n">
-        <v>58119</v>
+        <v>58126</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 22559-2026 artfynd.xlsx
+++ b/artfynd/A 22559-2026 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>133930757</v>
       </c>
       <c r="B3" t="n">
-        <v>101376</v>
+        <v>101386</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>133930852</v>
       </c>
       <c r="B4" t="n">
-        <v>58126</v>
+        <v>58136</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 22559-2026 artfynd.xlsx
+++ b/artfynd/A 22559-2026 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>133930757</v>
       </c>
       <c r="B3" t="n">
-        <v>101386</v>
+        <v>101388</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 22559-2026 artfynd.xlsx
+++ b/artfynd/A 22559-2026 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>133930757</v>
       </c>
       <c r="B3" t="n">
-        <v>101389</v>
+        <v>101396</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 22559-2026 artfynd.xlsx
+++ b/artfynd/A 22559-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -791,48 +791,53 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133930757</v>
+        <v>133930852</v>
       </c>
       <c r="B3" t="n">
-        <v>101396</v>
+        <v>58136</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Grankärret, Grankärret, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>555719</v>
+        <v>555700</v>
       </c>
       <c r="R3" t="n">
-        <v>6337493</v>
+        <v>6337491</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -888,53 +893,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133930852</v>
+        <v>133930757</v>
       </c>
       <c r="B4" t="n">
-        <v>58136</v>
+        <v>101403</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Grankärret, Grankärret, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>555700</v>
+        <v>555719</v>
       </c>
       <c r="R4" t="n">
-        <v>6337491</v>
+        <v>6337493</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -987,6 +987,103 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>133930820</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100806</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222584</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Bergsslok</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Melica nutans</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Grankärret, Grankärret, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>555701</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6337493</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22559-2026 artfynd.xlsx
+++ b/artfynd/A 22559-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133477377</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133930852</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,6 +1002,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133930757</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1084,8 +1104,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133930820</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>